--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$47</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="344">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -621,6 +621,96 @@
     <t>.code</t>
   </si>
   <si>
+    <t>PractitionerRole.code.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
@@ -708,39 +798,7 @@
     <t>PractitionerRole.telecom.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>PractitionerRole.telecom.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.system</t>
@@ -1342,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.26953125" customWidth="true" bestFit="true"/>
@@ -3218,7 +3276,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>194</v>
       </c>
@@ -3234,25 +3292,25 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3279,52 +3337,52 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AM17" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3332,14 +3390,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3355,18 +3413,20 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3403,19 +3463,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3427,27 +3487,27 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
-      <c r="A19" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3461,25 +3521,29 @@
         <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3527,7 +3591,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3570,7 +3634,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>89</v>
@@ -3582,15 +3646,17 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
         <v>219</v>
       </c>
@@ -3641,13 +3707,13 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -3656,10 +3722,10 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3668,12 +3734,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3684,25 +3750,25 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3729,13 +3795,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -3753,28 +3819,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3782,14 +3848,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3805,20 +3871,18 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>135</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3855,19 +3919,19 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3879,27 +3943,27 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3910,25 +3974,25 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3955,52 +4019,52 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4022,7 +4086,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>89</v>
@@ -4034,17 +4098,15 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>247</v>
       </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>248</v>
       </c>
@@ -4095,13 +4157,13 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
@@ -4110,13 +4172,13 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>250</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4124,10 +4186,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4144,26 +4206,22 @@
         <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4187,13 +4245,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4211,7 +4269,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>198</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4223,16 +4281,16 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4240,21 +4298,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4263,19 +4321,19 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>201</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>137</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4313,37 +4371,37 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4352,12 +4410,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4371,7 +4429,7 @@
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
@@ -4380,13 +4438,13 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4413,13 +4471,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4437,7 +4495,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4446,30 +4504,30 @@
         <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4480,30 +4538,32 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>195</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4551,13 +4611,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -4566,13 +4626,13 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4580,10 +4640,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4600,22 +4660,26 @@
         <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>222</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -4639,13 +4703,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4663,7 +4727,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4675,16 +4739,16 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4699,14 +4763,14 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4715,19 +4779,19 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>135</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>228</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>137</v>
+        <v>287</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4777,25 +4841,25 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4806,46 +4870,42 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4893,28 +4953,28 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>294</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -4922,10 +4982,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4948,15 +5008,17 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>296</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -4981,13 +5043,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5005,7 +5067,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5023,7 +5085,7 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5034,10 +5096,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5060,13 +5122,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
+        <v>197</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5117,7 +5179,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>198</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5129,13 +5191,13 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>281</v>
+        <v>199</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5146,21 +5208,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5172,16 +5234,16 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>301</v>
+        <v>137</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5231,25 +5293,25 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>205</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>281</v>
+        <v>199</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5260,44 +5322,46 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5345,25 +5409,25 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5374,10 +5438,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5400,13 +5464,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>277</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5433,13 +5497,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5457,7 +5521,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5475,7 +5539,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5486,10 +5550,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5512,13 +5576,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>155</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
+        <v>315</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5569,7 +5633,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5581,13 +5645,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5598,21 +5662,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5624,16 +5688,16 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>134</v>
+        <v>317</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>135</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>137</v>
+        <v>320</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5683,25 +5747,25 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5712,46 +5776,44 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>317</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -5799,25 +5861,25 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>131</v>
+        <v>300</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5828,10 +5890,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5839,10 +5901,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -5854,13 +5916,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>222</v>
+        <v>296</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5911,13 +5973,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -5929,7 +5991,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5940,10 +6002,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5966,13 +6028,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>197</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6023,7 +6085,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6035,13 +6097,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>281</v>
+        <v>199</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6052,21 +6114,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6078,15 +6140,17 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
+        <v>135</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6135,25 +6199,25 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>281</v>
+        <v>199</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6164,14 +6228,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6184,23 +6248,25 @@
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>321</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>324</v>
+        <v>143</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6249,7 +6315,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6261,23 +6327,473 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AK44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN43">
+  <autoFilter ref="A1:AN47">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6287,7 +6803,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI42">
+  <conditionalFormatting sqref="A2:AI46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitionerrole.xlsx
+++ b/dev/StructureDefinition-ph-core-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
